--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0060.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0060.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Tụi ta đã cố tìm nhưng vẫn chưa thấy ai giống mô tả của cô ấy. Chắc cô ấy đang ẩn mình thôi.</t>
+          <t>Tụi tao đã cố tìm nhưng vẫn chưa thấy ai giống mô tả của cô ấy. Chắc cô ấy đang ẩn mình thôi.</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Kem thì ta chịu thua thôi.</t>
+          <t>Kem thì tao chịu thua thôi.</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Ta có cần chuẩn bị gì không?</t>
+          <t>Tao có cần chuẩn bị gì không?</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Xin chào, {Male=ông;Female=bà} {PlayerName}.</t>
+          <t>Xin chào, {Male=Mr.;Female=Ms.} {PlayerName}.</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3759,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Nếu không có Kẻ Lang Thang Đêm Lửa, chắc chúng đã moi sạch túi ta rồi.</t>
+          <t>Nếu không có Kẻ Lang Thang Đêm Lửa, chắc chúng đã moi sạch túi tao rồi.</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Từ khi thành phố an toàn hơn, ta chẳng còn nghe mấy tin tức về bọn chúng nữa.</t>
+          <t>Từ khi thành phố an toàn hơn, tao chẳng còn nghe mấy tin tức về bọn chúng nữa.</t>
         </is>
       </c>
     </row>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Nhiều người bị nhắm đến, nhưng cuối cùng họ lại chỉ cử ngươi đi giải quyết à?</t>
+          <t>Nhiều người bị nhắm đến, nhưng cuối cùng họ lại chỉ cử mày đi giải quyết à?</t>
         </is>
       </c>
     </row>
@@ -6359,7 +6359,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Vấn đề lớn nhất mà ta thấy là...</t>
+          <t>Vấn đề lớn nhất mà tao thấy là...</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Chắc là cậu đang giấu ta điều gì đó phải không?</t>
+          <t>Chắc là cậu đang giấu tao điều gì đó phải không?</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Được rồi, được rồi... Bản năng nhạy bén đấy. Ở bên cậu lâu thế này, ta chẳng còn bí mật gì nữa.</t>
+          <t>Được rồi, được rồi... Bản năng nhạy bén đấy. Ở bên cậu lâu thế này, tao chẳng còn bí mật gì nữa.</t>
         </is>
       </c>
     </row>
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Chuyện gì đã xảy ra?</t>
+          <t>Chuyện gì đã xảy ra thế?</t>
         </is>
       </c>
     </row>
@@ -8374,7 +8374,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Vậy thì ta sẽ chơi tới cùng.</t>
+          <t>Vậy thì tao sẽ chơi tới cùng.</t>
         </is>
       </c>
     </row>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Ui da... Cậu đánh mạnh hơn ta tưởng...</t>
+          <t>Ui da... Cậu đánh mạnh hơn tao tưởng...</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Trời đất, sao cậu di chuyển nhanh thế hả?!</t>
+          <t>Trời đất, sao mày di chuyển nhanh thế hả?!</t>
         </is>
       </c>
     </row>
@@ -9999,7 +9999,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Không đời nào! Giờ nó là con tin của ta rồi... Đây là vụ Echonapping, nghe chưa!</t>
+          <t>Không đời nào! Giờ nó là con tin của tao rồi... Đây là vụ Echonapping, nghe chưa!</t>
         </is>
       </c>
     </row>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Ăn cắp, dối trá, lừa đảo, cướp bóc... vẫn y như ngày xưa. Hãy dâng lễ vật cho bà ta, nếu không... hoặc ngươi sẽ bị đánh tơi tả.</t>
+          <t>Ăn cắp, dối trá, lừa đảo, cướp bóc... vẫn y như ngày xưa. Hãy dâng lễ vật cho bà ta, nếu không... hoặc mày sẽ bị đánh tơi tả.</t>
         </is>
       </c>
     </row>
@@ -11754,7 +11754,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Tại sao?</t>
+          <t>Sao vậy?</t>
         </is>
       </c>
     </row>
@@ -13964,7 +13964,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Ta sẽ gây chú ý phía trước. Phần trình diễn để ta lo.</t>
+          <t>Tao sẽ gây chú ý phía trước. Phần trình diễn để tao lo.</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Giờ ngươi đã bắt được ta rồi, chống cự làm gì cho thêm đau. Càng kéo dài, càng tự chuốc lấy khổ thôi.</t>
+          <t>Giờ mày đã bắt được tao rồi, chống cự làm gì cho thêm đau. Càng kéo dài, càng tự chuốc lấy khổ thôi.</t>
         </is>
       </c>
     </row>
@@ -15589,7 +15589,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Tin ta đi, giờ ta thà chết chứ không muốn đứng đây thay vì nằm trên giường.</t>
+          <t>Tin tao đi, giờ tao thà chết chứ không muốn đứng đây thay vì nằm trên giường.</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Ta đã từng cảm ơn ai chân thành đến thế này chưa nhỉ?</t>
+          <t>Tao đã từng cảm ơn ai chân thành đến thế này chưa nhỉ?</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Lo việc của ngươi trước đi!</t>
+          <t>Lo việc của mày trước đi!</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Chỉ là việc thường ngày của ta thôi. Giống như ngủ nướng, ăn uống hay chải chuốt sừng với tóc ấy mà.</t>
+          <t>Chỉ là việc thường ngày của tao thôi. Giống như ngủ nướng, ăn uống hay chải chuốt sừng với tóc ấy mà.</t>
         </is>
       </c>
     </row>
@@ -20919,7 +20919,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Và cũng từ đó, rắc rối bắt đầu tìm đến ta.</t>
+          <t>Và cũng từ đó, rắc rối bắt đầu tìm đến tao.</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Ta cứ nghĩ, sao phải chờ nó tệ hơn? Xong nhanh thì hơn.</t>
+          <t>Tao cứ nghĩ, sao phải chờ nó tệ hơn? Xong nhanh thì hơn.</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Bản năng của cậu xuất phát từ thiện ý. Một nắm đấm có thể không sắc bén như lưỡi kiếm, nhưng vẫn đủ sức phá vỡ những vấn đề đã ăn sâu bén rễ.</t>
+          <t>Bản năng của bạn xuất phát từ thiện ý. Một nắm đấm có thể không sắc bén như lưỡi kiếm, nhưng vẫn đủ sức phá vỡ những vấn đề đã ăn sâu bén rễ.</t>
         </is>
       </c>
     </row>
@@ -21634,7 +21634,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Dọn dẹp mấy thứ tạp nham này chẳng thấm vào đâu với ta.</t>
+          <t>Dọn dẹp mấy thứ tạp nham này chẳng thấm vào đâu với tao.</t>
         </is>
       </c>
     </row>
@@ -22284,7 +22284,7 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>Ta đã cố làm điều đó từ lâu rồi, nhưng chính cậu mới là người biến nó thành hiện thực.</t>
+          <t>Tao đã cố làm điều đó từ lâu rồi, nhưng chính cậu mới là người biến nó thành hiện thực.</t>
         </is>
       </c>
     </row>
@@ -22609,7 +22609,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Ta đang nghĩ... thật nhẹ nhõm khi có người như ngươi sẵn sàng đứng ra gánh vác.</t>
+          <t>Tao đang nghĩ... thật nhẹ nhõm khi có người như mày sẵn sàng đứng ra gánh vác.</t>
         </is>
       </c>
     </row>
@@ -24039,7 +24039,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Giờ thì, đưa ta ít tiền đi nào, hả?</t>
+          <t>Giờ thì, đưa tao ít tiền đi nào, hả?</t>
         </is>
       </c>
     </row>
@@ -24364,7 +24364,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Ta đã bảo rồi mà, phải không? Ta bảo chúng nó cứng đầu lắm! Sao cậu chẳng bao giờ chịu nghe ta vậy?</t>
+          <t>Tao đã bảo rồi mà, phải không? Tao bảo chúng nó cứng đầu lắm! Sao cậu chẳng bao giờ chịu nghe tao vậy?</t>
         </is>
       </c>
     </row>
@@ -25274,7 +25274,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Cậu đã làm trò này bao nhiêu lần rồi?</t>
+          <t>Mày đã làm trò này bao nhiêu lần rồi?</t>
         </is>
       </c>
     </row>
@@ -25664,7 +25664,7 @@
       </c>
       <c r="M388" t="inlineStr">
         <is>
-          <t>Okay.</t>
+          <t>Ừ.</t>
         </is>
       </c>
     </row>
@@ -26574,7 +26574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Ta không biết cái tên đó.</t>
+          <t>Tao không biết cái tên đó.</t>
         </is>
       </c>
     </row>
@@ -26834,7 +26834,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Sao cơ?</t>
+          <t>Lại đến nữa à?</t>
         </is>
       </c>
     </row>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Kẻ Đi Bộ Đêm Cháy... Ugh, đừng bắt ta phải nhắc lại lần nữa.</t>
+          <t>Kẻ Đi Bộ Đêm Cháy... Ugh, đừng bắt tao phải nhắc lại lần nữa.</t>
         </is>
       </c>
     </row>
